--- a/data/my_data_class.xlsx
+++ b/data/my_data_class.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hannahmcnulty/Documents/github/McNultyBio_6100/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78FA250-374C-F943-BD41-98F7E55D0549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2246A2D0-4FF4-FE4C-9896-08CD674DB51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3480" yWindow="2660" windowWidth="27640" windowHeight="16680" xr2:uid="{E7091CFE-63CB-024B-BDEC-6497C8926BF7}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="107">
   <si>
     <t>Original Tree ID</t>
   </si>
@@ -358,6 +358,9 @@
   </si>
   <si>
     <t>sampling_event</t>
+  </si>
+  <si>
+    <t>dbh</t>
   </si>
 </sst>
 </file>
@@ -1037,6 +1040,9 @@
       <c r="K1" s="5" t="s">
         <v>105</v>
       </c>
+      <c r="L1" s="5" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
